--- a/output/roomself_excel/7876.xlsx
+++ b/output/roomself_excel/7876.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56133</v>
+        <v>119156</v>
       </c>
       <c r="D2" t="n">
-        <v>3224</v>
+        <v>3048</v>
       </c>
       <c r="E2" t="n">
-        <v>759</v>
+        <v>378</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50350</v>
+        <v>189449</v>
       </c>
       <c r="D3" t="n">
-        <v>1820</v>
+        <v>3572</v>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>579</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>255490</v>
+        <v>19557</v>
       </c>
       <c r="D4" t="n">
-        <v>5800</v>
+        <v>1120</v>
       </c>
       <c r="E4" t="n">
-        <v>761</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88803</v>
+        <v>31421</v>
       </c>
       <c r="D5" t="n">
-        <v>2416</v>
+        <v>1592</v>
       </c>
       <c r="E5" t="n">
-        <v>253</v>
+        <v>182</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>119228</v>
+        <v>80029</v>
       </c>
       <c r="D6" t="n">
-        <v>2876</v>
+        <v>3284</v>
       </c>
       <c r="E6" t="n">
-        <v>414</v>
+        <v>190</v>
       </c>
       <c r="F6" t="n">
-        <v>341</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80029</v>
+        <v>66041</v>
       </c>
       <c r="D7" t="n">
-        <v>3284</v>
+        <v>2972</v>
       </c>
       <c r="E7" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19557</v>
+        <v>21021</v>
       </c>
       <c r="D8" t="n">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31820</v>
+        <v>5434</v>
       </c>
       <c r="D9" t="n">
-        <v>1496</v>
+        <v>724</v>
       </c>
       <c r="E9" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>119156</v>
+        <v>50350</v>
       </c>
       <c r="D10" t="n">
-        <v>3048</v>
+        <v>1820</v>
       </c>
       <c r="E10" t="n">
-        <v>378</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>368</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>82814</v>
+        <v>56133</v>
       </c>
       <c r="D11" t="n">
-        <v>2616</v>
+        <v>3224</v>
       </c>
       <c r="E11" t="n">
-        <v>253</v>
+        <v>759</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21021</v>
+        <v>88803</v>
       </c>
       <c r="D12" t="n">
-        <v>1160</v>
+        <v>2416</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31421</v>
+        <v>119228</v>
       </c>
       <c r="D13" t="n">
-        <v>1592</v>
+        <v>2876</v>
       </c>
       <c r="E13" t="n">
-        <v>182</v>
+        <v>414</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11154</v>
+        <v>31820</v>
       </c>
       <c r="D14" t="n">
-        <v>940</v>
+        <v>1496</v>
       </c>
       <c r="E14" t="n">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5434</v>
+        <v>82814</v>
       </c>
       <c r="D15" t="n">
-        <v>724</v>
+        <v>2616</v>
       </c>
       <c r="E15" t="n">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11154</v>
+      </c>
+      <c r="D16" t="n">
+        <v>940</v>
+      </c>
+      <c r="E16" t="n">
+        <v>187</v>
+      </c>
+      <c r="F16" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/7876.xlsx
+++ b/output/roomself_excel/7876.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3048</v>
       </c>
-      <c r="E2" t="n">
-        <v>378</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>368</v>
+        <v>357</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>346</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3572</v>
       </c>
-      <c r="E3" t="n">
-        <v>579</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>370</v>
+        <v>546</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>347</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,12 @@
       <c r="D4" t="n">
         <v>1120</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>1592</v>
       </c>
-      <c r="E5" t="n">
-        <v>182</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>37</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>164</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +631,26 @@
       <c r="D6" t="n">
         <v>3284</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>425</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>190</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>26</v>
       </c>
     </row>
@@ -585,11 +669,27 @@
       <c r="D7" t="n">
         <v>2972</v>
       </c>
-      <c r="E7" t="n">
-        <v>203</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>51</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>185</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +707,12 @@
       <c r="D8" t="n">
         <v>1160</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>724</v>
       </c>
-      <c r="E9" t="n">
-        <v>143</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +759,27 @@
       <c r="D10" t="n">
         <v>1820</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>190</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>15</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>265</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +797,27 @@
       <c r="D11" t="n">
         <v>3224</v>
       </c>
-      <c r="E11" t="n">
-        <v>759</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>154</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>729</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +835,20 @@
       <c r="D12" t="n">
         <v>2416</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>253</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>23</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +865,27 @@
       <c r="D13" t="n">
         <v>2876</v>
       </c>
-      <c r="E13" t="n">
-        <v>414</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>341</v>
+        <v>396</v>
+      </c>
+      <c r="G13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>323</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +903,20 @@
       <c r="D14" t="n">
         <v>1496</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>165</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>18</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +933,20 @@
       <c r="D15" t="n">
         <v>2616</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>253</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>26</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +963,27 @@
       <c r="D16" t="n">
         <v>940</v>
       </c>
-      <c r="E16" t="n">
-        <v>187</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>66</v>
+      </c>
+      <c r="J16" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/7876.xlsx
+++ b/output/roomself_excel/7876.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,26 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +537,22 @@
       <c r="J2" t="n">
         <v>21</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>147</v>
+      </c>
+      <c r="N2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -554,6 +590,22 @@
       </c>
       <c r="J3" t="n">
         <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>190</v>
+      </c>
+      <c r="N3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -577,6 +629,10 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -615,6 +671,22 @@
       <c r="J5" t="n">
         <v>18</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>91</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -653,6 +725,10 @@
       <c r="J6" t="n">
         <v>26</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,6 +767,10 @@
       <c r="J7" t="n">
         <v>21</v>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -713,6 +793,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -743,6 +827,22 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>92</v>
+      </c>
+      <c r="N9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -781,6 +881,10 @@
       <c r="J10" t="n">
         <v>12</v>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -819,6 +923,10 @@
       <c r="J11" t="n">
         <v>12</v>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -849,6 +957,22 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>91</v>
+      </c>
+      <c r="N12" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -887,6 +1011,22 @@
       <c r="J13" t="n">
         <v>18</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>136</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -917,6 +1057,22 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>88</v>
+      </c>
+      <c r="N14" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -947,6 +1103,22 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -985,6 +1157,10 @@
       <c r="J16" t="n">
         <v>18</v>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
